--- a/data/manuscript_data/real_datasets_source.xlsx
+++ b/data/manuscript_data/real_datasets_source.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
   <si>
     <t>study</t>
   </si>
@@ -171,6 +171,18 @@
   </si>
   <si>
     <t>Cell Host &amp; Microbe</t>
+  </si>
+  <si>
+    <t>GMHI</t>
+  </si>
+  <si>
+    <t>A predictive index for health status using species-level gut microbiome profiling</t>
+  </si>
+  <si>
+    <t>Gupta (2020)</t>
+  </si>
+  <si>
+    <t>Nature Communications</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1330,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1494,6 +1506,20 @@
         <v>47</v>
       </c>
     </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
